--- a/preorder_forms/037_winter_collection_pre_order_form--preorder_forms.xlsx
+++ b/preorder_forms/037_winter_collection_pre_order_form--preorder_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'standard_shipping',_'label':_'standard_shipping',_'value':_'standard_shipping'}</t>
+          <t>standard_shipping</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Standard Shipping', 'label': 'Standard Shipping', 'value': 'Standard Shipping'}</t>
+          <t>Standard Shipping</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'express_shipping',_'label':_'express_shipping',_'value':_'express_shipping'}</t>
+          <t>express_shipping</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Express Shipping', 'label': 'Express Shipping', 'value': 'Express Shipping'}</t>
+          <t>Express Shipping</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'credit_card',_'label':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Credit Card', 'label': 'Credit Card', 'value': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bank_transfer',_'label':_'bank_transfer',_'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bank Transfer', 'label': 'Bank Transfer', 'value': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending',_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pending', 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'processing',_'label':_'processing',_'value':_'processing'}</t>
+          <t>processing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Processing', 'label': 'Processing', 'value': 'Processing'}</t>
+          <t>Processing</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'shipped',_'label':_'shipped',_'value':_'shipped'}</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Shipped', 'label': 'Shipped', 'value': 'Shipped'}</t>
+          <t>Shipped</t>
         </is>
       </c>
     </row>
